--- a/src/src/main/webapp/portal/acquisition/plan/Acquisition_Import_Template.xlsx
+++ b/src/src/main/webapp/portal/acquisition/plan/Acquisition_Import_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProjectCodes\hc-apm-web\src\src\main\webapp\portal\acquisition\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F74E72-A2F8-4418-83ED-3233326CFA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3FC5E7-3D4B-4CDA-BDCA-6179EDE0D766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>预算单价（万元）</t>
   </si>
   <si>
-    <t>预算总价（万元）</t>
-  </si>
-  <si>
     <t>预计使用年限（年）</t>
   </si>
   <si>
@@ -70,14 +67,6 @@
   </si>
   <si>
     <t>新增人员配备（人）</t>
-  </si>
-  <si>
-    <t>折旧成本
-（万元）</t>
-  </si>
-  <si>
-    <t>维保费用
-（万元）</t>
   </si>
   <si>
     <t>配套不可单独收费耗材收费占比及采购成本（万元）</t>
@@ -97,6 +86,18 @@
   </si>
   <si>
     <t>申报单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>预算总价（万元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>折旧成本（万元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>维保费用（万元）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +540,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="36">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -557,55 +558,55 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="W1" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.4">
